--- a/app/templates/report/bookdocs.xlsx
+++ b/app/templates/report/bookdocs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE77C8B-D83A-4835-B2B9-A304A71C380E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F57C202-A9DB-4D2D-AED0-0FE841646E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reservas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Reservas!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Reservas!$A$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Motivo</t>
   </si>
@@ -62,6 +62,9 @@
   <si>
     <t>Fecha
 hasta</t>
+  </si>
+  <si>
+    <t>Recurso</t>
   </si>
 </sst>
 </file>
@@ -189,15 +192,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -575,29 +570,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="24.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="24.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="68.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="24.88671875" style="1"/>
+    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="68.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="24.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="4"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="5" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -605,32 +602,36 @@
         <v>4</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="11" t="s">
-        <v>1</v>
-      </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="11" t="s">
+        <v>1</v>
+      </c>
       <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:G2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
